--- a/data/satisfaction_detail/2026/1-6月/会议主承办.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/会议主承办.xlsx
@@ -475,7 +475,7 @@
         <v>9.51</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +488,7 @@
         <v>9.9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -540,7 +540,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="9">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         <v>9.81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.74</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="13">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>9.92</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="18">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>9.960000000000001</v>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>9.960000000000001</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9.75</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="21">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.58</v>
+        <v>9.56</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>9.85</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="23">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>9.81</v>
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9.630000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>9.5</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="26">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.85</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="27">
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9.77</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="29">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>9.67</v>
+        <v>9.68</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.76</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="30">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.57</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="31">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>9.91</v>
+        <v>9.92</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.82</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="32">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>9.83</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>9.81</v>
